--- a/data/douban_top250_full.xlsx
+++ b/data/douban_top250_full.xlsx
@@ -471,22 +471,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>73251896人评价</t>
+          <t>73251968人评价</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>...1994</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>犯罪 剧情</t>
         </is>
       </c>
     </row>
@@ -501,22 +501,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62399710人评价</t>
+          <t>62399742人评价</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>张丰毅 Fengyi Zha...1993</t>
+          <t>中国大陆 中国香港</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>中国大陆 中国香港</t>
+          <t>剧情 爱情 同性</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>52471898人评价</t>
+          <t>52471936人评价</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -561,22 +561,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52408518人评价</t>
+          <t>52408542人评价</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>...1994</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -591,22 +591,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>42511259人评价</t>
+          <t>42511306人评价</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>入野自由 Miy...2001</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 动画 奇幻</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51468577人评价</t>
+          <t>51468602人评价</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>42152793人评价</t>
+          <t>42152854人评价</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -681,22 +681,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>42532204人评价</t>
+          <t>42532235人评价</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>娜塔莉·波特曼 ...1994</t>
+          <t>法国 美国</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>法国 美国</t>
+          <t>剧情 动作 犯罪</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>42303302人评价</t>
+          <t>42303334人评价</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>41993633人评价</t>
+          <t>41993667人评价</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>劳拉·琳妮 Lau...1998</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 科幻</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>51236857人评价</t>
+          <t>51236873人评价</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>41530605人评价</t>
+          <t>41530633人评价</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -831,22 +831,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31863262人评价</t>
+          <t>31863318人评价</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>...1998</t>
+          <t>意大利</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>意大利</t>
+          <t>剧情 音乐</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>32287860人评价</t>
+          <t>32287920人评价</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>瑞奇·摩尔 Rich Moore   主演: 金妮弗·...2016</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 动画 冒险</t>
         </is>
       </c>
     </row>
@@ -891,22 +891,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>22059806人评价</t>
+          <t>22059836人评价</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>卡...2009</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>剧情 喜剧 爱情 歌舞</t>
         </is>
       </c>
     </row>
@@ -921,22 +921,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>31475475人评价</t>
+          <t>31475499人评价</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>艾丽...2008</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>科幻 动画 冒险</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>31459802人评价</t>
+          <t>31459835人评价</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -981,22 +981,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>31548182人评价</t>
+          <t>31548206人评价</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>麦兆辉   主演: 刘德华 Andy Lau</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>梁朝伟 Tony Leung Chiu W...2002</t>
+          <t>剧情 犯罪 惊悚</t>
         </is>
       </c>
     </row>
@@ -1011,22 +1011,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6728802人评价</t>
+          <t>6728823人评价</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>玛琳·...1957</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 犯罪 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -1041,22 +1041,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21695476人评价</t>
+          <t>21695496人评价</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>吴孟达 Man Tat Ng...1995</t>
+          <t>中国香港 中国大陆</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>中国香港 中国大陆</t>
+          <t>喜剧 爱情 奇幻 古装</t>
         </is>
       </c>
     </row>
@@ -1071,22 +1071,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>31028138人评价</t>
+          <t>31028142人评价</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>郑有美 Yu-mi Jung</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>...2011</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -1101,22 +1101,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11960955人评价</t>
+          <t>11960991人评价</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>阿德里安·莫利纳 Adrian Molina   主演: ...2017</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 动画 奇幻 音乐</t>
         </is>
       </c>
     </row>
@@ -1131,22 +1131,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>31281769人评价</t>
+          <t>31281783人评价</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>艾力克·托兰达 Eric Toledano   主...2011</t>
+          <t>法国</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>剧情 喜剧</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>31095346人评价</t>
+          <t>31095360人评价</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>31018235人评价</t>
+          <t>31018252人评价</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>陈...1987</t>
+          <t>法国</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>英国 意大利 中国大陆 法国</t>
+          <t>剧情 传记 历史</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11673925人评价</t>
+          <t>11673949人评价</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1251,22 +1251,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21405500人评价</t>
+          <t>21405529人评价</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Emma Watson</t>
+          <t>美国 英国</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rupert Grint2001</t>
+          <t>奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -1281,22 +1281,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21399491人评价</t>
+          <t>21399503人评价</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>坂本千夏 Ch...1988</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3960839人评价</t>
+          <t>3960848人评价</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>巩俐 Li Gong</t>
+          <t>中国大陆 中国香港</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>姜武 Wu Jiang1994</t>
+          <t>剧情 历史 家庭</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12033797人评价</t>
+          <t>12033830人评价</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>卡...2010</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 喜剧 爱情</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21182704人评价</t>
+          <t>21182718人评价</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1401,22 +1401,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3901740人评价</t>
+          <t>3901750人评价</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>西恩...2003</t>
+          <t>美国 新西兰</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>美国 新西兰</t>
+          <t>剧情 动作 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -1431,22 +1431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>02332238人评价</t>
+          <t>02332260人评价</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>王传君 Chuanjun Wang</t>
+          <t>中国大陆</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>周...2018</t>
+          <t>剧情 喜剧</t>
         </is>
       </c>
     </row>
@@ -1461,22 +1461,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3785779人评价</t>
+          <t>3785788人评价</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>乔治·库克 George Cukor   主演: 费...1939</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 历史 爱情 战争</t>
         </is>
       </c>
     </row>
@@ -1491,22 +1491,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01904711人评价</t>
+          <t>01904740人评价</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>葛优 You Ge</t>
+          <t>中国大陆 中国香港</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>周润发 Yun-F...2010</t>
+          <t>剧情 喜剧 动作 西部</t>
         </is>
       </c>
     </row>
@@ -1521,22 +1521,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>11485432人评价</t>
+          <t>11485446人评价</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>鲍勃·彼德森 Bob Peterson   主演: 爱德...2009</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 喜剧 动画 冒险</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1551,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>11275631人评价</t>
+          <t>11275660人评价</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>木村拓...2004</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>爱情 动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -1581,22 +1581,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4571983人评价</t>
+          <t>4571989人评价</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>马丁...1957</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -1611,22 +1611,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3767686人评价</t>
+          <t>3767704人评价</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>...2015</t>
+          <t>德国 瑞士</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>德国 瑞士</t>
+          <t>剧情 冒险 家庭</t>
         </is>
       </c>
     </row>
@@ -1641,22 +1641,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3769431人评价</t>
+          <t>3769443人评价</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>严志媛 Ji-won Uhm ...2013</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>11196564人评价</t>
+          <t>11196585人评价</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1701,22 +1701,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>21000200人评价</t>
+          <t>21000216人评价</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>横泽启子 Ke...1986</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -1731,22 +1731,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3708517人评价</t>
+          <t>3708525人评价</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>香川照之 Teruyuki Kagawa</t>
+          <t>中国大陆</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>...2000</t>
+          <t>剧情 喜剧</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01731320人评价</t>
+          <t>01731340人评价</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>法缇玛...2016</t>
+          <t>印度</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>印度</t>
+          <t>剧情 传记 运动 家庭</t>
         </is>
       </c>
     </row>
@@ -1791,22 +1791,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>11479107人评价</t>
+          <t>11479124人评价</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>伊尔凡·可汗 Irrfan...2012</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>美国 中国台湾 英国 加拿大</t>
+          <t>剧情 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3742461人评价</t>
+          <t>3742476人评价</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>英国 法国 波兰 德国 美国</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1851,22 +1851,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2848994人评价</t>
+          <t>2849007人评价</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>西恩...2002</t>
+          <t>美国 新西兰</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>美国 新西兰</t>
+          <t>剧情 动作 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -1881,22 +1881,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2869544人评价</t>
+          <t>2869558人评价</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>罗伯...1989</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -1911,22 +1911,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01354107人评价</t>
+          <t>01354127人评价</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>吴孟达 Man Tat Ng...1995</t>
+          <t>中国香港 中国大陆</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>中国香港 中国大陆</t>
+          <t>喜剧 爱情 奇幻 古装</t>
         </is>
       </c>
     </row>
@@ -1941,22 +1941,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>11154586人评价</t>
+          <t>11154597人评价</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>...2018</t>
+          <t>英国</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>黎巴嫩 美国 法国 塞浦路斯 卡塔尔 英国</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -1971,22 +1971,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>91874357人评价</t>
+          <t>91874384人评价</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>...2018</t>
+          <t>美国 中国大陆</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>美国 中国大陆</t>
+          <t>剧情 喜剧 传记 音乐</t>
         </is>
       </c>
     </row>
@@ -2001,22 +2001,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>11013307人评价</t>
+          <t>11013317人评价</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>克里斯...1992</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -2031,22 +2031,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>4504624人评价</t>
+          <t>4504635人评价</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>富润生 Runsheng Fu...1961(中国大陆)</t>
+          <t>中国大陆</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1964(中国大陆)</t>
+          <t>剧情 动画 奇幻 古装</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1941057人评价</t>
+          <t>1941063人评价</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>拉娜·沃卓斯基 Lana Wachowski   主...1999</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>动作 科幻</t>
         </is>
       </c>
     </row>
@@ -2096,17 +2096,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>西恩...2001</t>
+          <t>新西兰 美国</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>新西兰 美国</t>
+          <t>剧情 动作 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2121,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>11040814人评价</t>
+          <t>11040825人评价</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>格...1953</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3632880人评价</t>
+          <t>3632889人评价</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1952258人评价</t>
+          <t>1952270人评价</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>罗伯·明可夫 Rob Minkoff   主演: 乔纳森·泰勒·托马...1994</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>动画 冒险 歌舞</t>
         </is>
       </c>
     </row>
@@ -2241,22 +2241,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2717068人评价</t>
+          <t>2717080人评价</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>杨贵媚 Kuei-Mei Yang</t>
+          <t>中国台湾 美国</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>吴...1994</t>
+          <t>剧情 家庭</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>金英爱 Yeong-ae...2013</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -2301,22 +2301,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01096278人评价</t>
+          <t>01096284人评价</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>凯特·布...2008</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 爱情 奇幻</t>
         </is>
       </c>
     </row>
@@ -2331,22 +2331,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0963796人评价</t>
+          <t>0963808人评价</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>布拉...1999</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 动作 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -2361,22 +2361,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1848037人评价</t>
+          <t>1848046人评价</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>艾德·哈...2001</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>传记 剧情</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2636583人评价</t>
+          <t>2636588人评价</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2421,22 +2421,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>91312879人评价</t>
+          <t>91312896人评价</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>丰川悦司 Ets...1995</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0961890人评价</t>
+          <t>0961925人评价</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1670985人评价</t>
+          <t>1670992人评价</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>德克斯特...1998</t>
+          <t>英国</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>剧情 喜剧 犯罪</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2627529人评价</t>
+          <t>2627532人评价</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2541,22 +2541,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1678437人评价</t>
+          <t>1678441人评价</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>克...1965</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 传记 爱情 歌舞</t>
         </is>
       </c>
     </row>
@@ -2571,22 +2571,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>91322164人评价</t>
+          <t>91322185人评价</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>元秋 Qiu Yuen</t>
+          <t>中国大陆 中国香港</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>...2004</t>
+          <t>动作 喜剧 犯罪 奇幻</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>91085931人评价</t>
+          <t>91085938人评价</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0881814人评价</t>
+          <t>0881830人评价</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>81574119人评价</t>
+          <t>81574140人评价</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>81428579人评价</t>
+          <t>81428593人评价</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>阿...2016</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>剧情 犯罪 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1719515人评价</t>
+          <t>1719530人评价</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2751,22 +2751,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>91007549人评价</t>
+          <t>91007559人评价</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>安...1991</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 犯罪 惊悚</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2460075人评价</t>
+          <t>2460090人评价</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2811,22 +2811,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>91075645人评价</t>
+          <t>91075665人评价</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>...2014</t>
+          <t>美国 德国 英国</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>美国 德国 英国</t>
+          <t>剧情 喜剧 冒险</t>
         </is>
       </c>
     </row>
@@ -2841,22 +2841,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>91059080人评价</t>
+          <t>91059095人评价</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>J·麦基·格鲁伯 J. Mackye Gruber   主...2004</t>
+          <t>美国 加拿大</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>美国 加拿大</t>
+          <t>剧情 悬疑 科幻 惊悚</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1599633人评价</t>
+          <t>1599639人评价</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2901,22 +2901,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>91103656人评价</t>
+          <t>91103664人评价</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>...2010</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3353253人评价</t>
+          <t>3353276人评价</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0808959人评价</t>
+          <t>0808967人评价</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>罗宾·...1997</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9957457人评价</t>
+          <t>9957467人评价</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9951021人评价</t>
+          <t>9951036人评价</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3051,22 +3051,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0716295人评价</t>
+          <t>0716305人评价</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>马西...2011</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -3081,22 +3081,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9907711人评价</t>
+          <t>9907728人评价</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>艾玛...2002</t>
+          <t>英国 美国</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>英国 美国</t>
+          <t>奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -3111,22 +3111,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1501025人评价</t>
+          <t>1501041人评价</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>李凯莉 Kelly Lee</t>
+          <t>中国台湾 日本</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>金燕玲 Elai...2000</t>
+          <t>剧情 爱情 家庭</t>
         </is>
       </c>
     </row>
@@ -3141,22 +3141,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>81086382人评价</t>
+          <t>81086393人评价</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>李力持 Lik-Chi Lee   主演: 周星驰 Stephen Ch...1999</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>喜剧 剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3343678人评价</t>
+          <t>3343679人评价</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>9829345人评价</t>
+          <t>9829357人评价</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>金相庆 Sang-kyun...2003</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>剧情 动作 犯罪 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -3231,22 +3231,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>9939075人评价</t>
+          <t>9939088人评价</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>雷...2003</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -3261,22 +3261,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0705372人评价</t>
+          <t>0705378人评价</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>梁朝伟 Tony Leu...1997</t>
+          <t>中国香港 日本 韩国</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>中国香港 日本 韩国</t>
+          <t>剧情 爱情 同性</t>
         </is>
       </c>
     </row>
@@ -3291,22 +3291,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>8961553人评价</t>
+          <t>8961567人评价</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>...2003</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>动作 冒险 奇幻</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3380907人评价</t>
+          <t>3380908人评价</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1468057人评价</t>
+          <t>1468058人评价</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3381,22 +3381,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>0563733人评价</t>
+          <t>0563742人评价</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>江守彻 Toru...2006</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动画 悬疑 科幻 惊悚</t>
         </is>
       </c>
     </row>
@@ -3411,22 +3411,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>81054085人评价</t>
+          <t>81054093人评价</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>布...1995</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 犯罪 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -3441,22 +3441,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>81215865人评价</t>
+          <t>81215891人评价</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>巩俐 Li Gong</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>陈...1993</t>
+          <t>喜剧 爱情 古装</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1465557人评价</t>
+          <t>1465562人评价</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3501,22 +3501,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>9664283人评价</t>
+          <t>9664295人评价</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>石田百合...1997</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -3531,22 +3531,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>9666697人评价</t>
+          <t>9666713人评价</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>张曼玉 Maggie Cheung</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>...1996</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -3561,22 +3561,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>81537727人评价</t>
+          <t>81537735人评价</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>李善均 Seon-gyun...2019</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>9808810人评价</t>
+          <t>9808819人评价</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3621,22 +3621,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2331221人评价</t>
+          <t>2331228人评价</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>钱运达 Yunda Qian   主演: 丁建华 Jianhua Din...1983(中国大陆)</t>
+          <t>中国大陆</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>动画 奇幻</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>9618409人评价</t>
+          <t>9618421人评价</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>朴信惠 Shi...2013</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>剧情 喜剧 家庭</t>
         </is>
       </c>
     </row>
@@ -3681,22 +3681,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>81137373人评价</t>
+          <t>81137416人评价</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>克里斯·威廉姆斯 Chris Williams   主演: 斯科特...2014</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 动作 科幻 动画 冒险</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>9632275人评价</t>
+          <t>9632282人评价</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>8793672人评价</t>
+          <t>8793683人评价</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3771,22 +3771,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>6205178人评价</t>
+          <t>6205187人评价</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>郑榕 Rong Zhen</t>
+          <t>中国大陆</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>蓝天野 T...1982(中国大陆)</t>
+          <t>剧情 历史</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>9648358人评价</t>
+          <t>9648365人评价</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3831,22 +3831,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>8771483人评价</t>
+          <t>8771497人评价</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>瑛太 E...2006</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 歌舞</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>8917390人评价</t>
+          <t>8917400人评价</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>金城武 Takeshi K...1994</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -3921,22 +3921,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1421078人评价</t>
+          <t>1421085人评价</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>松本梨香 Rica Matsu...1997</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 犯罪 动画 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -3951,22 +3951,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>8798111人评价</t>
+          <t>8798127人评价</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>罗纳尔多·德尔·卡门 Ronaldo Del Carmen  &amp;nb...2015</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 动画 冒险</t>
         </is>
       </c>
     </row>
@@ -3981,22 +3981,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>9624141人评价</t>
+          <t>9624148人评价</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>神木...2010</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -4011,22 +4011,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>9740025人评价</t>
+          <t>9740029人评价</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>...2008</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -4041,22 +4041,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>9670064人评价</t>
+          <t>9670072人评价</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>关口雄介 Yus...1999</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 喜剧</t>
         </is>
       </c>
     </row>
@@ -4071,22 +4071,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>8778337人评价</t>
+          <t>8778350人评价</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>杰克·吉伦哈尔 Jake...2005</t>
+          <t>美国 加拿大</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>美国 加拿大</t>
+          <t>剧情 爱情 同性 家庭</t>
         </is>
       </c>
     </row>
@@ -4101,22 +4101,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>71116210人评价</t>
+          <t>71116215人评价</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>薇诺娜·...1990</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 爱情 奇幻</t>
         </is>
       </c>
     </row>
@@ -4131,22 +4131,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>9603261人评价</t>
+          <t>9603264人评价</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>苏菲·玛...1995</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>动作 传记 剧情 历史 战争</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>8786123人评价</t>
+          <t>8786135人评价</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4191,22 +4191,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>71066981人评价</t>
+          <t>71066993人评价</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>罗莎蒙...2014</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 犯罪 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -4221,22 +4221,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1369984人评价</t>
+          <t>1369990人评价</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>北浦爱...2004</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -4251,22 +4251,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>8831833人评价</t>
+          <t>8831843人评价</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>王祖贤 Joey W...1987</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>爱情 奇幻 武侠 古装</t>
         </is>
       </c>
     </row>
@@ -4281,22 +4281,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>8858956人评价</t>
+          <t>8858974人评价</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>克里斯·桑德斯 Chris Sanders   主演:...2010</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -4311,22 +4311,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>7925181人评价</t>
+          <t>7925197人评价</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>马修·...2005</t>
+          <t>法国 英国 美国</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>法国 英国 美国</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -4341,22 +4341,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>8798639人评价</t>
+          <t>8798652人评价</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>梁朝伟 Tony Leu...2000</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -4371,22 +4371,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>9523262人评价</t>
+          <t>9523270人评价</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>崔岷植 Min-sik...2013</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>剧情 犯罪</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1358313人评价</t>
+          <t>1358316人评价</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>9588778人评价</t>
+          <t>9588787人评价</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>蒂姆·艾...2010</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>9564667人评价</t>
+          <t>9564675人评价</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4491,22 +4491,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>8692171人评价</t>
+          <t>8692175人评价</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>宁静 Jing Ning</t>
+          <t>中国大陆 中国香港</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>陶虹 Hong Tao1994</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -4521,22 +4521,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>7954228人评价</t>
+          <t>7954251人评价</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>汤唯 Wei Tang</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>...2007</t>
+          <t>剧情 爱情 情色</t>
         </is>
       </c>
     </row>
@@ -4551,22 +4551,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>0471202人评价</t>
+          <t>0471203人评价</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>三浦贵大 Takahir...2014</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>71017731人评价</t>
+          <t>71017736人评价</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>8765742人评价</t>
+          <t>8765747人评价</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>大卫·斯沃曼 David Silverman   主演: 约...2001</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>儿童 喜剧 动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>0429351人评价</t>
+          <t>0429353人评价</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4671,22 +4671,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>9518067人评价</t>
+          <t>9518074人评价</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>小林桂树 K...1995</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 爱情 动画</t>
         </is>
       </c>
     </row>
@@ -4706,17 +4706,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>严定宪 Dingxian Yan   主演: 梁正晖 Zhenghui ...1979</t>
+          <t>中国大陆</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>中国大陆</t>
+          <t>冒险 动画 奇幻</t>
         </is>
       </c>
     </row>
@@ -4731,22 +4731,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>8818915人评价</t>
+          <t>8818927人评价</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>...2017</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>意大利 法国 巴西 美国</t>
+          <t>剧情 爱情 同性</t>
         </is>
       </c>
     </row>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>8788570人评价</t>
+          <t>8788582人评价</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>吴孟达 Man Tat Ng</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>...1994</t>
+          <t>剧情 喜剧 古装</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>8638314人评价</t>
+          <t>8638321人评价</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4821,22 +4821,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>8687355人评价</t>
+          <t>8687362人评价</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>...2012</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 动作 西部 冒险</t>
         </is>
       </c>
     </row>
@@ -4851,22 +4851,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>61343008人评价</t>
+          <t>61343025人评价</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>郑有美 Yu-mi Jung</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>马...2016</t>
+          <t>动作 惊悚 灾难</t>
         </is>
       </c>
     </row>
@@ -4886,17 +4886,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>克里斯·雷纳德 Chris Renaud   主演: ...2010</t>
+          <t>美国 法国</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>美国 法国</t>
+          <t>喜剧 动画 冒险</t>
         </is>
       </c>
     </row>
@@ -4911,22 +4911,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0418639人评价</t>
+          <t>0418641人评价</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>三浦贵大 Takahir...2015</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -4941,22 +4941,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0428181人评价</t>
+          <t>0428186人评价</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>归亚蕾 Ya-lei Kuei</t>
+          <t>中国台湾 美国</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>郎...1993</t>
+          <t>剧情 喜剧 爱情 同性 家庭</t>
         </is>
       </c>
     </row>
@@ -4971,22 +4971,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>8607102人评价</t>
+          <t>8607107人评价</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>内山昂辉 K...2011</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 爱情 动画 奇幻</t>
         </is>
       </c>
     </row>
@@ -5006,17 +5006,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>冈田将生 ...2010</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 悬疑</t>
         </is>
       </c>
     </row>
@@ -5031,22 +5031,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0467762人评价</t>
+          <t>0467766人评价</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>菲利...2009</t>
+          <t>澳大利亚 美国</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>澳大利亚 美国</t>
+          <t>剧情 喜剧 动画</t>
         </is>
       </c>
     </row>
@@ -5061,22 +5061,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>3233691人评价</t>
+          <t>3233693人评价</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>志村乔 ...1954</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动作 冒险 剧情</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>61509090人评价</t>
+          <t>61509102人评价</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5151,22 +5151,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>8624222人评价</t>
+          <t>8624227人评价</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>阿...2003</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 爱情 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0353326人评价</t>
+          <t>0353330人评价</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5211,22 +5211,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>7714743人评价</t>
+          <t>7714749人评价</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>林青霞 Bri...1993</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>喜剧 奇幻 武侠 古装</t>
         </is>
       </c>
     </row>
@@ -5241,22 +5241,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>7856150人评价</t>
+          <t>7856163人评价</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>...2016</t>
+          <t>澳大利亚 美国</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>澳大利亚 美国</t>
+          <t>剧情 传记 历史 战争</t>
         </is>
       </c>
     </row>
@@ -5276,17 +5276,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>凯普·鲍尔斯 Kemp Powers   主演: 杰米·...2020</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>动画 奇幻 音乐</t>
         </is>
       </c>
     </row>
@@ -5301,22 +5301,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>51584854人评价</t>
+          <t>51584881人评价</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>上...2016</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 爱情 动画</t>
         </is>
       </c>
     </row>
@@ -5336,17 +5336,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>杨亚洲 Yazhou Yang   主演: 牛振华 Zhenhua N...1994</t>
+          <t>中国大陆 中国香港</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>中国大陆 中国香港</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -5361,22 +5361,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0374627人评价</t>
+          <t>0374630人评价</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dakota Fanning</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mi...2001</t>
+          <t>剧情 家庭</t>
         </is>
       </c>
     </row>
@@ -5391,22 +5391,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>8635968人评价</t>
+          <t>8635973人评价</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>闵孝琳 Hy...2011</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>剧情 喜剧</t>
         </is>
       </c>
     </row>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>李璟荣 Kyeong-y...2013</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>剧情 犯罪 悬疑</t>
         </is>
       </c>
     </row>
@@ -5451,22 +5451,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>8495083人评价</t>
+          <t>8495085人评价</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>莉莉·沃卓斯基 Lilly Wachowski   ...2003</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>动作 科幻</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>1424927人评价</t>
+          <t>1424959人评价</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>71121335人评价</t>
+          <t>71121345人评价</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>7915773人评价</t>
+          <t>7915779人评价</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5571,22 +5571,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9468274人评价</t>
+          <t>9468282人评价</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>...2007</t>
+          <t>英国</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>美国 德国 法国 英国</t>
+          <t>动作 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -5601,22 +5601,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>7609370人评价</t>
+          <t>7609379人评价</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>加利·艾...2004</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>悬疑 惊悚 恐怖</t>
         </is>
       </c>
     </row>
@@ -5631,22 +5631,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>8563505人评价</t>
+          <t>8563517人评价</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>麦兆辉 Alan Mak   主演: 陈冠希 Edison Chen</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>...2003</t>
+          <t>剧情 犯罪 惊悚</t>
         </is>
       </c>
     </row>
@@ -5661,22 +5661,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0342118人评价</t>
+          <t>0342127人评价</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>苏...1991</t>
+          <t>美国 英国 法国</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>美国 英国 法国</t>
+          <t>犯罪 剧情 惊悚</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>8503744人评价</t>
+          <t>8503746人评价</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5721,22 +5721,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>5156168人评价</t>
+          <t>5156173人评价</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>唐国强 Guoqiang Tang</t>
+          <t>中国大陆</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>何...1984(中国大陆)</t>
+          <t>剧情 战争</t>
         </is>
       </c>
     </row>
@@ -5751,22 +5751,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>7917497人评价</t>
+          <t>7917508人评价</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>克里斯·桑德斯 Chris Sanders   主演...2013</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 动画 冒险</t>
         </is>
       </c>
     </row>
@@ -5781,22 +5781,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>9386093人评价</t>
+          <t>9386101人评价</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>...1999</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>犯罪 剧情 奇幻 悬疑</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>9470192人评价</t>
+          <t>9470198人评价</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5841,22 +5841,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>6921399人评价</t>
+          <t>6921409人评价</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>刘桦 Hua Liu</t>
+          <t>中国大陆 中国香港</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>连晋 Teddy Lin2006</t>
+          <t>喜剧 犯罪</t>
         </is>
       </c>
     </row>
@@ -5871,22 +5871,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>8518171人评价</t>
+          <t>8518185人评价</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>长泽雅美 M...2015</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 家庭</t>
         </is>
       </c>
     </row>
@@ -5906,17 +5906,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>吉恩·凯利 Gene Kelly   主演: 吉恩·...1952</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 歌舞 爱情</t>
         </is>
       </c>
     </row>
@@ -5931,22 +5931,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>9392793人评价</t>
+          <t>9392798人评价</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>...1968</t>
+          <t>英国 美国</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>英国 美国</t>
+          <t>科幻 惊悚 冒险</t>
         </is>
       </c>
     </row>
@@ -5961,22 +5961,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>9392205人评价</t>
+          <t>9392208人评价</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>松田洋治 Y...1984</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -5991,22 +5991,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0332175人评价</t>
+          <t>0332178人评价</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>卡迪亚·兰德 Kátia Lund  &amp;nbsp...2002</t>
+          <t>巴西 法国</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>巴西 法国</t>
+          <t>犯罪 剧情</t>
         </is>
       </c>
     </row>
@@ -6021,22 +6021,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>7613584人评价</t>
+          <t>7613593人评价</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>王笑天 Xiaotian Wang ...2014</t>
+          <t>中国大陆</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>中国大陆</t>
+          <t>剧情 犯罪 悬疑</t>
         </is>
       </c>
     </row>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>6603787人评价</t>
+          <t>6603792人评价</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>狄龙 Lung Ti</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>张国...1986</t>
+          <t>剧情 动作 犯罪</t>
         </is>
       </c>
     </row>
@@ -6081,22 +6081,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>7666183人评价</t>
+          <t>7666189人评价</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>...2000</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>犯罪 剧情 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -6111,22 +6111,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>8471866人评价</t>
+          <t>8471871人评价</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>张国荣 Leslie Cheung...1991</t>
+          <t>中国香港</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>中国香港</t>
+          <t>剧情 喜剧 动作 犯罪</t>
         </is>
       </c>
     </row>
@@ -6141,22 +6141,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>7609367人评价</t>
+          <t>7609372人评价</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>萨拉...2012</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -6176,17 +6176,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>苏菲·奥...2004</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>英国 南非 意大利 美国</t>
+          <t>剧情 传记 历史 战争</t>
         </is>
       </c>
     </row>
@@ -6201,22 +6201,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>7892290人评价</t>
+          <t>7892295人评价</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>安藤樱 Sa...2018</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 犯罪 家庭</t>
         </is>
       </c>
     </row>
@@ -6236,17 +6236,17 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>梅垣义明 Yoshiaki Ume...2003</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 喜剧 动画</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>5984394人评价</t>
+          <t>5984408人评价</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -6291,22 +6291,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>9366220人评价</t>
+          <t>9366225人评价</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>杨静怡 Lisa Yang</t>
+          <t>中国台湾</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>张...1991</t>
+          <t>剧情 犯罪</t>
         </is>
       </c>
     </row>
@@ -6321,22 +6321,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>7683366人评价</t>
+          <t>7683375人评价</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>克里斯·韦奇 Chris Wedge   主演...2002</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 动画 冒险</t>
         </is>
       </c>
     </row>
@@ -6351,22 +6351,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>7522116人评价</t>
+          <t>7522117人评价</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>佐久间玲 Re...1989</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -6381,22 +6381,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>3188166人评价</t>
+          <t>3188168人评价</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>姜文 Wen Jiang</t>
+          <t>中国大陆</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>郑在石...1987</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -6411,22 +6411,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2217722人评价</t>
+          <t>2217723人评价</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>...1987</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -6441,22 +6441,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>7611335人评价</t>
+          <t>7611338人评价</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>任达华 Simon Yam</t>
+          <t>中国香港 中国大陆</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>钟绍...2010</t>
+          <t>剧情 家庭</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>7514754人评价</t>
+          <t>7514759人评价</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -6501,22 +6501,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>7535085人评价</t>
+          <t>7535095人评价</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>摩根...2007</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>冒险 喜剧 剧情</t>
         </is>
       </c>
     </row>
@@ -6531,22 +6531,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>7550559人评价</t>
+          <t>7550566人评价</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>陈竹昇 Chu-sh...2017</t>
+          <t>中国台湾</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>中国台湾</t>
+          <t>剧情 喜剧</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>...2011</t>
+          <t>美国 加拿大</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>美国 加拿大</t>
+          <t>科幻 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -6591,22 +6591,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>6819346人评价</t>
+          <t>6819369人评价</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>有村架纯 Kasu...2021</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -6621,22 +6621,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>7615726人评价</t>
+          <t>7615731人评价</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>查理兹·塞...2015</t>
+          <t>澳大利亚 美国</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>澳大利亚 美国</t>
+          <t>动作 科幻 冒险</t>
         </is>
       </c>
     </row>
@@ -6651,22 +6651,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>9374053人评价</t>
+          <t>9374060人评价</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>爱河...2010</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 动画 儿童</t>
         </is>
       </c>
     </row>
@@ -6681,22 +6681,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>6804862人评价</t>
+          <t>6804866人评价</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>洛芙琳·坦丹 Loveleen Tandan   主演: 戴夫...2008</t>
+          <t>英国</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>英国</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -6711,22 +6711,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>9344244人评价</t>
+          <t>9344248人评价</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>张磊 Lei Zhang</t>
+          <t>中国大陆 中国香港</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>亓亮 Qi L...2004</t>
+          <t>剧情 犯罪</t>
         </is>
       </c>
     </row>
@@ -6741,22 +6741,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>6640706人评价</t>
+          <t>6640721人评价</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>克里斯汀·...2013</t>
+          <t>美国 英国</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>美国 英国</t>
+          <t>剧情 喜剧 冒险</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>3171697人评价</t>
+          <t>3171698人评价</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6801,22 +6801,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>6686947人评价</t>
+          <t>6686956人评价</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>本·哈...2018</t>
+          <t>英国 美国</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>英国 美国</t>
+          <t>剧情 传记 同性 音乐</t>
         </is>
       </c>
     </row>
@@ -6836,17 +6836,17 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>...2014</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 音乐</t>
         </is>
       </c>
     </row>
@@ -6861,22 +6861,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>6633422人评价</t>
+          <t>6633428人评价</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>林青霞 Brigitte...1994</t>
+          <t>中国香港 中国台湾</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>中国香港 中国台湾</t>
+          <t>剧情 动作 爱情 武侠 古装</t>
         </is>
       </c>
     </row>
@@ -6891,22 +6891,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>6598923人评价</t>
+          <t>6598931人评价</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>王祖贤 Joey Wang</t>
+          <t>中国香港 中国大陆</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>...1993</t>
+          <t>剧情 爱情 奇幻 古装</t>
         </is>
       </c>
     </row>
@@ -6921,22 +6921,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>41090917人评价</t>
+          <t>41090931人评价</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>...2016</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 爱情 歌舞</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>6691530人评价</t>
+          <t>6691541人评价</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6981,22 +6981,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>7558482人评价</t>
+          <t>7558487人评价</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>...2009</t>
+          <t>德国 美国</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>德国 美国</t>
+          <t>剧情 犯罪</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>8383500人评价</t>
+          <t>8383504人评价</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>6844384人评价</t>
+          <t>6844403人评价</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -7071,22 +7071,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>8368011人评价</t>
+          <t>8368023人评价</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>马精武 Jingwu Ma</t>
+          <t>中国台湾</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>何赛...1991</t>
+          <t>剧情</t>
         </is>
       </c>
     </row>
@@ -7101,22 +7101,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>7506591人评价</t>
+          <t>7506597人评价</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>林青霞 Brigitte ...1992</t>
+          <t>中国香港 中国大陆</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>中国香港 中国大陆</t>
+          <t>动作 爱情 武侠 古装</t>
         </is>
       </c>
     </row>
@@ -7131,22 +7131,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>51049106人评价</t>
+          <t>51049127人评价</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>华森·波克彭...2010</t>
+          <t>泰国</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>泰国</t>
+          <t>剧情 喜剧 爱情</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>7500014人评价</t>
+          <t>7500016人评价</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -7191,22 +7191,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>8348102人评价</t>
+          <t>8348106人评价</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>乌玛...1997</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 科幻 惊悚</t>
         </is>
       </c>
     </row>
@@ -7221,22 +7221,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>6572543人评价</t>
+          <t>6572548人评价</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>土井洋辉 Hir...2008</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动画 奇幻 冒险</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>7441756人评价</t>
+          <t>7441759人评价</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>9294236人评价</t>
+          <t>9294239人评价</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>6691132人评价</t>
+          <t>6691140人评价</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>8356690人评价</t>
+          <t>8356691人评价</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>京町子 ...1950</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 犯罪 悬疑</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>6679874人评价</t>
+          <t>6679886人评价</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>6648698人评价</t>
+          <t>6648704人评价</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -7431,22 +7431,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>5745122人评价</t>
+          <t>5745124人评价</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>...2004</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>5806094人评价</t>
+          <t>5806100人评价</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>连姆...2003</t>
+          <t>英国 美国 法国</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>英国 美国 法国</t>
+          <t>喜剧 剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -7491,22 +7491,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>5828056人评价</t>
+          <t>5828066人评价</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>杰西卡...2015</t>
+          <t>约旦</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>英国 美国 匈牙利 约旦</t>
+          <t>剧情 科幻 冒险</t>
         </is>
       </c>
     </row>
@@ -7521,22 +7521,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>7453535人评价</t>
+          <t>7453542人评价</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>莉莉·沃卓斯基 Lilly Wachowski   ...2003</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>动作 科幻</t>
         </is>
       </c>
     </row>
@@ -7551,22 +7551,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>8325938人评价</t>
+          <t>8325943人评价</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>夏川结衣 Yu...2008</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>剧情 家庭</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6598835人评价</t>
+          <t>6598834人评价</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -7611,22 +7611,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>8316283人评价</t>
+          <t>8316285人评价</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>小山茉美 Mam...2001</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动画 剧情 爱情</t>
         </is>
       </c>
     </row>
@@ -7641,22 +7641,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>5822324人评价</t>
+          <t>5822342人评价</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>珍妮弗·李 Jennifer Lee   主演: 克里斯汀...2013</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>喜剧 动画 奇幻 歌舞</t>
         </is>
       </c>
     </row>
@@ -7671,22 +7671,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>7413784人评价</t>
+          <t>7413786人评价</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>...2005</t>
+          <t>美国 德国</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>美国 德国</t>
+          <t>剧情 犯罪</t>
         </is>
       </c>
     </row>
@@ -7701,22 +7701,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>7397694人评价</t>
+          <t>7397701人评价</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>...2004</t>
+          <t>美国 德国</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>美国 德国</t>
+          <t>动作 悬疑 惊悚</t>
         </is>
       </c>
     </row>
@@ -7731,22 +7731,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6753722人评价</t>
+          <t>6753731人评价</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>彼得·拉姆齐 Peter Ramsey   主...2018</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>动作 科幻 动画 冒险</t>
         </is>
       </c>
     </row>
@@ -7761,22 +7761,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>0216327人评价</t>
+          <t>0216330人评价</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>大冢明夫 Akio...1995</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>动作 科幻 动画</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>7420381人评价</t>
+          <t>7420383人评价</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7821,22 +7821,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>8309473人评价</t>
+          <t>8309477人评价</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>罗伯特·...1940</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>剧情 爱情 战争</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>9269831人评价</t>
+          <t>9269838人评价</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7881,22 +7881,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>5570389人评价</t>
+          <t>5570407人评价</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>金泰梨 Tae-ri K...2016</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>剧情 悬疑 情色 同性</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>7398858人评价</t>
+          <t>7398860人评价</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>爱尔兰 加拿大 英国 美国</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -7941,22 +7941,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>6553315人评价</t>
+          <t>6553339人评价</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>吴可熙 Wu K...2017</t>
+          <t>中国台湾</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>中国台湾</t>
+          <t>剧情 悬疑</t>
         </is>
       </c>
     </row>
